--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_rios.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_rios.xlsx
@@ -362,42 +362,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>E_PRENETA_a</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>E_BASNETA_a</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>E_MEDIANETA_a</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>E_SUPNETA_a</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>E_PREBRUT_a</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>E_PRENETA_a</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>E_BASBRUT_a</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>E_BASNETA_a</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>E_MEDIABRUT_a</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>E_MEDIANETA_a</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>E_SUPBRUT_a</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>E_SUPNETA_a</t>
         </is>
       </c>
     </row>
@@ -408,28 +408,28 @@
         </is>
       </c>
       <c r="B2">
+        <v>62.58898</v>
+      </c>
+      <c r="C2">
+        <v>96.07819000000001</v>
+      </c>
+      <c r="D2">
+        <v>84.59545</v>
+      </c>
+      <c r="E2">
+        <v>46.02341</v>
+      </c>
+      <c r="F2">
         <v>62.91414</v>
       </c>
-      <c r="C2">
-        <v>62.58898</v>
-      </c>
-      <c r="D2">
+      <c r="G2">
         <v>101.3654</v>
       </c>
-      <c r="E2">
-        <v>96.07819000000001</v>
-      </c>
-      <c r="F2">
+      <c r="H2">
         <v>108.4913</v>
       </c>
-      <c r="G2">
-        <v>84.59545</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
         <v>72.30374</v>
-      </c>
-      <c r="I2">
-        <v>46.02341</v>
       </c>
     </row>
     <row r="3">
@@ -439,28 +439,28 @@
         </is>
       </c>
       <c r="B3">
+        <v>58.91892</v>
+      </c>
+      <c r="C3">
+        <v>96.53979</v>
+      </c>
+      <c r="D3">
+        <v>86.58147</v>
+      </c>
+      <c r="E3">
+        <v>31.85484</v>
+      </c>
+      <c r="F3">
         <v>59.18919</v>
       </c>
-      <c r="C3">
-        <v>58.91892</v>
-      </c>
-      <c r="D3">
+      <c r="G3">
         <v>101.7301</v>
       </c>
-      <c r="E3">
-        <v>96.53979</v>
-      </c>
-      <c r="F3">
+      <c r="H3">
         <v>104.4728</v>
       </c>
-      <c r="G3">
-        <v>86.58147</v>
-      </c>
-      <c r="H3">
+      <c r="I3">
         <v>46.97581</v>
-      </c>
-      <c r="I3">
-        <v>31.85484</v>
       </c>
     </row>
     <row r="4">
@@ -470,28 +470,28 @@
         </is>
       </c>
       <c r="B4">
+        <v>65.27558999999999</v>
+      </c>
+      <c r="C4">
+        <v>97.01205</v>
+      </c>
+      <c r="D4">
+        <v>89.13444</v>
+      </c>
+      <c r="E4">
+        <v>37.48686</v>
+      </c>
+      <c r="F4">
         <v>65.43307</v>
       </c>
-      <c r="C4">
-        <v>65.27558999999999</v>
-      </c>
-      <c r="D4">
+      <c r="G4">
         <v>100.5301</v>
       </c>
-      <c r="E4">
-        <v>97.01205</v>
-      </c>
-      <c r="F4">
+      <c r="H4">
         <v>101.8416</v>
       </c>
-      <c r="G4">
-        <v>89.13444</v>
-      </c>
-      <c r="H4">
+      <c r="I4">
         <v>56.36172</v>
-      </c>
-      <c r="I4">
-        <v>37.48686</v>
       </c>
     </row>
     <row r="5">
@@ -501,28 +501,28 @@
         </is>
       </c>
       <c r="B5">
+        <v>61.17136</v>
+      </c>
+      <c r="C5">
+        <v>96.34820000000001</v>
+      </c>
+      <c r="D5">
+        <v>86.86709</v>
+      </c>
+      <c r="E5">
+        <v>32.64574</v>
+      </c>
+      <c r="F5">
         <v>61.38829</v>
       </c>
-      <c r="C5">
-        <v>61.17136</v>
-      </c>
-      <c r="D5">
+      <c r="G5">
         <v>100.552</v>
       </c>
-      <c r="E5">
-        <v>96.34820000000001</v>
-      </c>
-      <c r="F5">
+      <c r="H5">
         <v>99.05064</v>
       </c>
-      <c r="G5">
-        <v>86.86709</v>
-      </c>
-      <c r="H5">
+      <c r="I5">
         <v>46.05381</v>
-      </c>
-      <c r="I5">
-        <v>32.64574</v>
       </c>
     </row>
     <row r="6">
@@ -532,28 +532,28 @@
         </is>
       </c>
       <c r="B6">
+        <v>67.66467</v>
+      </c>
+      <c r="C6">
+        <v>96.09644</v>
+      </c>
+      <c r="D6">
+        <v>82.85078</v>
+      </c>
+      <c r="E6">
+        <v>34.3342</v>
+      </c>
+      <c r="F6">
         <v>67.86427</v>
       </c>
-      <c r="C6">
-        <v>67.66467</v>
-      </c>
-      <c r="D6">
+      <c r="G6">
         <v>101.7222</v>
       </c>
-      <c r="E6">
-        <v>96.09644</v>
-      </c>
-      <c r="F6">
+      <c r="H6">
         <v>101.559</v>
       </c>
-      <c r="G6">
-        <v>82.85078</v>
-      </c>
-      <c r="H6">
+      <c r="I6">
         <v>53.00261</v>
-      </c>
-      <c r="I6">
-        <v>34.3342</v>
       </c>
     </row>
     <row r="7">
@@ -566,25 +566,25 @@
         <v>62.56529</v>
       </c>
       <c r="C7">
+        <v>96.57607</v>
+      </c>
+      <c r="D7">
+        <v>84.47893999999999</v>
+      </c>
+      <c r="E7">
+        <v>31.4405</v>
+      </c>
+      <c r="F7">
         <v>62.56529</v>
       </c>
-      <c r="D7">
+      <c r="G7">
         <v>101.5531</v>
       </c>
-      <c r="E7">
-        <v>96.57607</v>
-      </c>
-      <c r="F7">
+      <c r="H7">
         <v>100.0739</v>
       </c>
-      <c r="G7">
-        <v>84.47893999999999</v>
-      </c>
-      <c r="H7">
+      <c r="I7">
         <v>45.51148</v>
-      </c>
-      <c r="I7">
-        <v>31.4405</v>
       </c>
     </row>
     <row r="8">
@@ -597,25 +597,25 @@
         <v>66.91627</v>
       </c>
       <c r="C8">
+        <v>96.15546999999999</v>
+      </c>
+      <c r="D8">
+        <v>88.17377</v>
+      </c>
+      <c r="E8">
+        <v>34.68531</v>
+      </c>
+      <c r="F8">
         <v>66.91627</v>
       </c>
-      <c r="D8">
+      <c r="G8">
         <v>101.3942</v>
       </c>
-      <c r="E8">
-        <v>96.15546999999999</v>
-      </c>
-      <c r="F8">
+      <c r="H8">
         <v>109.4127</v>
       </c>
-      <c r="G8">
-        <v>88.17377</v>
-      </c>
-      <c r="H8">
+      <c r="I8">
         <v>49.51049</v>
-      </c>
-      <c r="I8">
-        <v>34.68531</v>
       </c>
     </row>
     <row r="9">
@@ -625,28 +625,28 @@
         </is>
       </c>
       <c r="B9">
+        <v>54.59705</v>
+      </c>
+      <c r="C9">
+        <v>96.44842</v>
+      </c>
+      <c r="D9">
+        <v>88.14617</v>
+      </c>
+      <c r="E9">
+        <v>31.70867</v>
+      </c>
+      <c r="F9">
         <v>54.67272</v>
       </c>
-      <c r="C9">
-        <v>54.59705</v>
-      </c>
-      <c r="D9">
+      <c r="G9">
         <v>100.4107</v>
       </c>
-      <c r="E9">
-        <v>96.44842</v>
-      </c>
-      <c r="F9">
+      <c r="H9">
         <v>103.877</v>
       </c>
-      <c r="G9">
-        <v>88.14617</v>
-      </c>
-      <c r="H9">
+      <c r="I9">
         <v>46.71836</v>
-      </c>
-      <c r="I9">
-        <v>31.70867</v>
       </c>
     </row>
     <row r="10">
@@ -659,25 +659,25 @@
         <v>63.67456</v>
       </c>
       <c r="C10">
+        <v>96.61663</v>
+      </c>
+      <c r="D10">
+        <v>83.96013000000001</v>
+      </c>
+      <c r="E10">
+        <v>43.40556</v>
+      </c>
+      <c r="F10">
         <v>63.67456</v>
       </c>
-      <c r="D10">
+      <c r="G10">
         <v>100.9054</v>
       </c>
-      <c r="E10">
-        <v>96.61663</v>
-      </c>
-      <c r="F10">
+      <c r="H10">
         <v>108.2918</v>
       </c>
-      <c r="G10">
-        <v>83.96013000000001</v>
-      </c>
-      <c r="H10">
+      <c r="I10">
         <v>64.90815000000001</v>
-      </c>
-      <c r="I10">
-        <v>43.40556</v>
       </c>
     </row>
     <row r="11">
@@ -690,25 +690,25 @@
         <v>53.97951</v>
       </c>
       <c r="C11">
+        <v>97.00924000000001</v>
+      </c>
+      <c r="D11">
+        <v>87.3807</v>
+      </c>
+      <c r="E11">
+        <v>31.1391</v>
+      </c>
+      <c r="F11">
         <v>53.97951</v>
       </c>
-      <c r="D11">
+      <c r="G11">
         <v>102.7189</v>
       </c>
-      <c r="E11">
-        <v>97.00924000000001</v>
-      </c>
-      <c r="F11">
+      <c r="H11">
         <v>103.0753</v>
       </c>
-      <c r="G11">
-        <v>87.3807</v>
-      </c>
-      <c r="H11">
+      <c r="I11">
         <v>42.70177</v>
-      </c>
-      <c r="I11">
-        <v>31.1391</v>
       </c>
     </row>
     <row r="12">
@@ -718,28 +718,28 @@
         </is>
       </c>
       <c r="B12">
+        <v>53.78031</v>
+      </c>
+      <c r="C12">
+        <v>97.84945999999999</v>
+      </c>
+      <c r="D12">
+        <v>84.55007999999999</v>
+      </c>
+      <c r="E12">
+        <v>33.60489</v>
+      </c>
+      <c r="F12">
         <v>53.78032</v>
       </c>
-      <c r="C12">
-        <v>53.78031</v>
-      </c>
-      <c r="D12">
+      <c r="G12">
         <v>103.6738</v>
       </c>
-      <c r="E12">
-        <v>97.84945999999999</v>
-      </c>
-      <c r="F12">
+      <c r="H12">
         <v>102.5467</v>
       </c>
-      <c r="G12">
-        <v>84.55007999999999</v>
-      </c>
-      <c r="H12">
+      <c r="I12">
         <v>46.33401</v>
-      </c>
-      <c r="I12">
-        <v>33.60489</v>
       </c>
     </row>
     <row r="13">
@@ -749,28 +749,28 @@
         </is>
       </c>
       <c r="B13">
+        <v>61.02662</v>
+      </c>
+      <c r="C13">
+        <v>96.02970000000001</v>
+      </c>
+      <c r="D13">
+        <v>82.46888</v>
+      </c>
+      <c r="E13">
+        <v>37.6071</v>
+      </c>
+      <c r="F13">
         <v>61.35931</v>
       </c>
-      <c r="C13">
-        <v>61.02662</v>
-      </c>
-      <c r="D13">
+      <c r="G13">
         <v>102.9135</v>
       </c>
-      <c r="E13">
-        <v>96.02970000000001</v>
-      </c>
-      <c r="F13">
+      <c r="H13">
         <v>105.9647</v>
       </c>
-      <c r="G13">
-        <v>82.46888</v>
-      </c>
-      <c r="H13">
+      <c r="I13">
         <v>55.96695</v>
-      </c>
-      <c r="I13">
-        <v>37.6071</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_rios.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_rios.xlsx
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 19:43</t>
+    <t xml:space="preserve">2026-08-02 19:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_rios.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_rios.xlsx
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 19:41</t>
+    <t xml:space="preserve">2026-08-05 10:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_rios.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_rios.xlsx
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:34</t>
+    <t xml:space="preserve">2026-08-16 09:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_rios.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_rios.xlsx
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:46</t>
+    <t xml:space="preserve">2026-08-19 11:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_rios.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_rios.xlsx
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 11:40</t>
+    <t xml:space="preserve">2026-08-28 11:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_rios.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_rios.xlsx
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:23</t>
+    <t xml:space="preserve">2026-09-06 17:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
